--- a/Avwap_Tarama_240726.xlsx
+++ b/Avwap_Tarama_240726.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="693">
   <si>
     <t>Hisse</t>
   </si>
@@ -1540,9 +1540,6 @@
     <t>SOKM</t>
   </si>
   <si>
-    <t>SONME</t>
-  </si>
-  <si>
     <t>SRVGY</t>
   </si>
   <si>
@@ -1735,6 +1732,9 @@
     <t>VRGYO</t>
   </si>
   <si>
+    <t>VSNMD</t>
+  </si>
+  <si>
     <t>XU030</t>
   </si>
   <si>
@@ -2054,9 +2054,6 @@
   </si>
   <si>
     <t>Aşağı Kırılım(H1,H2,H3,L1,L3)</t>
-  </si>
-  <si>
-    <t>Direnç Retest(H1,H2,H3,L1,L2,L3)</t>
   </si>
   <si>
     <t>Yukarı Kırılım(L2) - Direnç Retest(H3,L3)</t>
@@ -2529,7 +2526,7 @@
         <v>594</v>
       </c>
       <c r="I2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J2">
         <v>3.33</v>
@@ -2658,7 +2655,7 @@
         <v>594</v>
       </c>
       <c r="I5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J5">
         <v>1.09</v>
@@ -2705,7 +2702,7 @@
         <v>595</v>
       </c>
       <c r="I6" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J6">
         <v>56.85</v>
@@ -2752,7 +2749,7 @@
         <v>594</v>
       </c>
       <c r="I7" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J7">
         <v>20.54</v>
@@ -2881,7 +2878,7 @@
         <v>596</v>
       </c>
       <c r="I10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J10">
         <v>33.81</v>
@@ -2928,7 +2925,7 @@
         <v>597</v>
       </c>
       <c r="I11" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J11">
         <v>3.06</v>
@@ -3016,7 +3013,7 @@
         <v>598</v>
       </c>
       <c r="I13" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J13">
         <v>20.28</v>
@@ -3186,7 +3183,7 @@
         <v>599</v>
       </c>
       <c r="I17" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J17">
         <v>2.83</v>
@@ -3233,7 +3230,7 @@
         <v>600</v>
       </c>
       <c r="I18" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J18">
         <v>73.81</v>
@@ -3444,7 +3441,7 @@
         <v>601</v>
       </c>
       <c r="I23" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J23">
         <v>11.56</v>
@@ -3532,7 +3529,7 @@
         <v>602</v>
       </c>
       <c r="I25" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J25">
         <v>9.359999999999999</v>
@@ -3620,7 +3617,7 @@
         <v>603</v>
       </c>
       <c r="I27" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J27">
         <v>2.66</v>
@@ -3708,7 +3705,7 @@
         <v>594</v>
       </c>
       <c r="I29" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J29">
         <v>8.41</v>
@@ -3755,7 +3752,7 @@
         <v>604</v>
       </c>
       <c r="I30" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J30">
         <v>833.72</v>
@@ -3884,7 +3881,7 @@
         <v>594</v>
       </c>
       <c r="I33" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J33">
         <v>5.73</v>
@@ -3931,7 +3928,7 @@
         <v>605</v>
       </c>
       <c r="I34" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J34">
         <v>10.81</v>
@@ -3978,7 +3975,7 @@
         <v>594</v>
       </c>
       <c r="I35" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J35">
         <v>18.29</v>
@@ -4066,7 +4063,7 @@
         <v>606</v>
       </c>
       <c r="I37" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J37">
         <v>72.64</v>
@@ -4113,7 +4110,7 @@
         <v>607</v>
       </c>
       <c r="I38" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J38">
         <v>16.55</v>
@@ -4283,7 +4280,7 @@
         <v>608</v>
       </c>
       <c r="I42" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="J42">
         <v>105.81</v>
@@ -4494,7 +4491,7 @@
         <v>609</v>
       </c>
       <c r="I47" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J47">
         <v>30.96</v>
@@ -4582,7 +4579,7 @@
         <v>610</v>
       </c>
       <c r="I49" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J49">
         <v>3.48</v>
@@ -4711,7 +4708,7 @@
         <v>611</v>
       </c>
       <c r="I52" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J52">
         <v>379.5</v>
@@ -4799,7 +4796,7 @@
         <v>594</v>
       </c>
       <c r="I54" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J54">
         <v>287.32</v>
@@ -4846,7 +4843,7 @@
         <v>594</v>
       </c>
       <c r="I55" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J55">
         <v>64.89</v>
@@ -5016,7 +5013,7 @@
         <v>612</v>
       </c>
       <c r="I59" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J59">
         <v>16.73</v>
@@ -5063,7 +5060,7 @@
         <v>613</v>
       </c>
       <c r="I60" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J60">
         <v>111.79</v>
@@ -5192,7 +5189,7 @@
         <v>605</v>
       </c>
       <c r="I63" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J63">
         <v>13.98</v>
@@ -5239,7 +5236,7 @@
         <v>594</v>
       </c>
       <c r="I64" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J64">
         <v>42.77</v>
@@ -5368,7 +5365,7 @@
         <v>594</v>
       </c>
       <c r="I67" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J67">
         <v>27.84</v>
@@ -5415,7 +5412,7 @@
         <v>614</v>
       </c>
       <c r="I68" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J68">
         <v>35.95</v>
@@ -5462,7 +5459,7 @@
         <v>615</v>
       </c>
       <c r="I69" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J69">
         <v>32.04</v>
@@ -5632,7 +5629,7 @@
         <v>616</v>
       </c>
       <c r="I73" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J73">
         <v>124.6</v>
@@ -5720,7 +5717,7 @@
         <v>594</v>
       </c>
       <c r="I75" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J75">
         <v>69.51000000000001</v>
@@ -5767,7 +5764,7 @@
         <v>617</v>
       </c>
       <c r="I76" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J76">
         <v>17.03</v>
@@ -5978,7 +5975,7 @@
         <v>618</v>
       </c>
       <c r="I81" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J81">
         <v>5.01</v>
@@ -6148,7 +6145,7 @@
         <v>619</v>
       </c>
       <c r="I85" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J85">
         <v>36.06</v>
@@ -6195,7 +6192,7 @@
         <v>620</v>
       </c>
       <c r="I86" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="J86">
         <v>29.43</v>
@@ -6283,7 +6280,7 @@
         <v>621</v>
       </c>
       <c r="I88" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J88">
         <v>23.77</v>
@@ -6412,7 +6409,7 @@
         <v>600</v>
       </c>
       <c r="I91" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J91">
         <v>250.69</v>
@@ -6459,7 +6456,7 @@
         <v>622</v>
       </c>
       <c r="I92" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J92">
         <v>381.54</v>
@@ -6506,7 +6503,7 @@
         <v>623</v>
       </c>
       <c r="I93" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J93">
         <v>177.81</v>
@@ -6553,7 +6550,7 @@
         <v>624</v>
       </c>
       <c r="I94" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J94">
         <v>10.05</v>
@@ -6641,7 +6638,7 @@
         <v>594</v>
       </c>
       <c r="I96" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J96">
         <v>28.62</v>
@@ -6811,7 +6808,7 @@
         <v>594</v>
       </c>
       <c r="I100" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J100">
         <v>17.41</v>
@@ -6858,7 +6855,7 @@
         <v>625</v>
       </c>
       <c r="I101" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J101">
         <v>43.53</v>
@@ -6946,7 +6943,7 @@
         <v>626</v>
       </c>
       <c r="I103" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J103">
         <v>19.37</v>
@@ -7075,7 +7072,7 @@
         <v>594</v>
       </c>
       <c r="I106" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J106">
         <v>6.64</v>
@@ -7204,7 +7201,7 @@
         <v>627</v>
       </c>
       <c r="I109" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J109">
         <v>8.69</v>
@@ -7333,7 +7330,7 @@
         <v>610</v>
       </c>
       <c r="I112" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J112">
         <v>13.43</v>
@@ -7380,7 +7377,7 @@
         <v>628</v>
       </c>
       <c r="I113" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J113">
         <v>577.0599999999999</v>
@@ -7591,7 +7588,7 @@
         <v>629</v>
       </c>
       <c r="I118" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J118">
         <v>43.36</v>
@@ -7761,7 +7758,7 @@
         <v>630</v>
       </c>
       <c r="I122" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J122">
         <v>40.5</v>
@@ -7808,7 +7805,7 @@
         <v>594</v>
       </c>
       <c r="I123" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J123">
         <v>1.62</v>
@@ -7855,7 +7852,7 @@
         <v>631</v>
       </c>
       <c r="I124" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="J124">
         <v>81.47</v>
@@ -8189,7 +8186,7 @@
         <v>632</v>
       </c>
       <c r="I132" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J132">
         <v>42.93</v>
@@ -8277,7 +8274,7 @@
         <v>618</v>
       </c>
       <c r="I134" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J134">
         <v>1767.52</v>
@@ -8324,7 +8321,7 @@
         <v>627</v>
       </c>
       <c r="I135" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J135">
         <v>1750.93</v>
@@ -8412,7 +8409,7 @@
         <v>633</v>
       </c>
       <c r="I137" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J137">
         <v>3.02</v>
@@ -8582,7 +8579,7 @@
         <v>634</v>
       </c>
       <c r="I141" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J141">
         <v>26.03</v>
@@ -8711,7 +8708,7 @@
         <v>600</v>
       </c>
       <c r="I144" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J144">
         <v>7.92</v>
@@ -8799,7 +8796,7 @@
         <v>594</v>
       </c>
       <c r="I146" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J146">
         <v>2.15</v>
@@ -8928,7 +8925,7 @@
         <v>594</v>
       </c>
       <c r="I149" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J149">
         <v>14.12</v>
@@ -9057,7 +9054,7 @@
         <v>594</v>
       </c>
       <c r="I152" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J152">
         <v>44.75</v>
@@ -9145,7 +9142,7 @@
         <v>635</v>
       </c>
       <c r="I154" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="J154">
         <v>104.3</v>
@@ -9192,7 +9189,7 @@
         <v>636</v>
       </c>
       <c r="I155" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J155">
         <v>36.44</v>
@@ -9239,7 +9236,7 @@
         <v>637</v>
       </c>
       <c r="I156" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J156">
         <v>24.9</v>
@@ -9409,7 +9406,7 @@
         <v>638</v>
       </c>
       <c r="I160" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J160">
         <v>9.02</v>
@@ -9579,7 +9576,7 @@
         <v>594</v>
       </c>
       <c r="I164" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J164">
         <v>33.99</v>
@@ -9626,7 +9623,7 @@
         <v>639</v>
       </c>
       <c r="I165" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J165">
         <v>165.37</v>
@@ -9714,7 +9711,7 @@
         <v>640</v>
       </c>
       <c r="I167" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J167">
         <v>21.45</v>
@@ -9761,7 +9758,7 @@
         <v>594</v>
       </c>
       <c r="I168" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J168">
         <v>25.82</v>
@@ -9849,7 +9846,7 @@
         <v>641</v>
       </c>
       <c r="I170" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J170">
         <v>124.65</v>
@@ -9896,7 +9893,7 @@
         <v>607</v>
       </c>
       <c r="I171" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J171">
         <v>4.69</v>
@@ -10189,7 +10186,7 @@
         <v>605</v>
       </c>
       <c r="I178" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J178">
         <v>346.55</v>
@@ -10236,7 +10233,7 @@
         <v>642</v>
       </c>
       <c r="I179" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J179">
         <v>19.03</v>
@@ -10447,7 +10444,7 @@
         <v>605</v>
       </c>
       <c r="I184" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J184">
         <v>17.05</v>
@@ -10494,7 +10491,7 @@
         <v>643</v>
       </c>
       <c r="I185" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J185">
         <v>110.71</v>
@@ -10582,7 +10579,7 @@
         <v>594</v>
       </c>
       <c r="I187" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J187">
         <v>3.27</v>
@@ -10752,7 +10749,7 @@
         <v>644</v>
       </c>
       <c r="I191" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J191">
         <v>6.69</v>
@@ -10840,7 +10837,7 @@
         <v>605</v>
       </c>
       <c r="I193" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J193">
         <v>23.87</v>
@@ -10887,7 +10884,7 @@
         <v>645</v>
       </c>
       <c r="I194" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="J194">
         <v>159.81</v>
@@ -10934,7 +10931,7 @@
         <v>594</v>
       </c>
       <c r="I195" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J195">
         <v>18.5</v>
@@ -10981,7 +10978,7 @@
         <v>646</v>
       </c>
       <c r="I196" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J196">
         <v>9.51</v>
@@ -11110,7 +11107,7 @@
         <v>610</v>
       </c>
       <c r="I199" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J199">
         <v>10.23</v>
@@ -11157,7 +11154,7 @@
         <v>605</v>
       </c>
       <c r="I200" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J200">
         <v>4.77</v>
@@ -11204,7 +11201,7 @@
         <v>647</v>
       </c>
       <c r="I201" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J201">
         <v>6.04</v>
@@ -11251,7 +11248,7 @@
         <v>594</v>
       </c>
       <c r="I202" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J202">
         <v>187.89</v>
@@ -11380,7 +11377,7 @@
         <v>603</v>
       </c>
       <c r="I205" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J205">
         <v>25.49</v>
@@ -11468,7 +11465,7 @@
         <v>648</v>
       </c>
       <c r="I207" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J207">
         <v>5.42</v>
@@ -11515,7 +11512,7 @@
         <v>610</v>
       </c>
       <c r="I208" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J208">
         <v>3.9</v>
@@ -11562,7 +11559,7 @@
         <v>630</v>
       </c>
       <c r="I209" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J209">
         <v>5.4</v>
@@ -11691,7 +11688,7 @@
         <v>649</v>
       </c>
       <c r="I212" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="J212">
         <v>9.710000000000001</v>
@@ -11820,7 +11817,7 @@
         <v>594</v>
       </c>
       <c r="I215" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J215">
         <v>5.87</v>
@@ -11867,7 +11864,7 @@
         <v>643</v>
       </c>
       <c r="I216" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J216">
         <v>2.88</v>
@@ -11996,7 +11993,7 @@
         <v>627</v>
       </c>
       <c r="I219" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J219">
         <v>13.66</v>
@@ -12207,7 +12204,7 @@
         <v>650</v>
       </c>
       <c r="I224" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J224">
         <v>2.56</v>
@@ -12254,7 +12251,7 @@
         <v>603</v>
       </c>
       <c r="I225" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J225">
         <v>39.07</v>
@@ -12506,7 +12503,7 @@
         <v>651</v>
       </c>
       <c r="I231" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J231">
         <v>6.92</v>
@@ -12553,7 +12550,7 @@
         <v>594</v>
       </c>
       <c r="I232" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J232">
         <v>33.61</v>
@@ -12600,7 +12597,7 @@
         <v>600</v>
       </c>
       <c r="I233" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J233">
         <v>9.039999999999999</v>
@@ -12647,7 +12644,7 @@
         <v>594</v>
       </c>
       <c r="I234" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J234">
         <v>7.5</v>
@@ -12694,7 +12691,7 @@
         <v>600</v>
       </c>
       <c r="I235" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J235">
         <v>38.66</v>
@@ -12741,7 +12738,7 @@
         <v>605</v>
       </c>
       <c r="I236" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J236">
         <v>67.56</v>
@@ -12993,7 +12990,7 @@
         <v>652</v>
       </c>
       <c r="I242" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J242">
         <v>42.04</v>
@@ -13204,7 +13201,7 @@
         <v>603</v>
       </c>
       <c r="I247" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J247">
         <v>315.76</v>
@@ -13251,7 +13248,7 @@
         <v>600</v>
       </c>
       <c r="I248" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J248">
         <v>243.82</v>
@@ -13298,7 +13295,7 @@
         <v>644</v>
       </c>
       <c r="I249" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J249">
         <v>13.8</v>
@@ -13468,7 +13465,7 @@
         <v>600</v>
       </c>
       <c r="I253" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J253">
         <v>28.41</v>
@@ -13515,7 +13512,7 @@
         <v>653</v>
       </c>
       <c r="I254" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J254">
         <v>69.06999999999999</v>
@@ -13685,7 +13682,7 @@
         <v>600</v>
       </c>
       <c r="I258" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J258">
         <v>3.22</v>
@@ -13773,7 +13770,7 @@
         <v>594</v>
       </c>
       <c r="I260" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J260">
         <v>3.67</v>
@@ -13984,7 +13981,7 @@
         <v>654</v>
       </c>
       <c r="I265" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J265">
         <v>3.78</v>
@@ -14031,7 +14028,7 @@
         <v>655</v>
       </c>
       <c r="I266" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J266">
         <v>3.74</v>
@@ -14078,7 +14075,7 @@
         <v>656</v>
       </c>
       <c r="I267" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J267">
         <v>7.42</v>
@@ -14166,7 +14163,7 @@
         <v>595</v>
       </c>
       <c r="I269" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J269">
         <v>5.6</v>
@@ -14213,7 +14210,7 @@
         <v>657</v>
       </c>
       <c r="I270" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J270">
         <v>4.3</v>
@@ -14424,7 +14421,7 @@
         <v>618</v>
       </c>
       <c r="I275" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J275">
         <v>2.07</v>
@@ -14471,7 +14468,7 @@
         <v>610</v>
       </c>
       <c r="I276" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J276">
         <v>1.72</v>
@@ -14969,7 +14966,7 @@
         <v>594</v>
       </c>
       <c r="I288" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J288">
         <v>59.51</v>
@@ -15057,7 +15054,7 @@
         <v>594</v>
       </c>
       <c r="I290" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J290">
         <v>23.9</v>
@@ -15186,7 +15183,7 @@
         <v>603</v>
       </c>
       <c r="I293" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J293">
         <v>8.890000000000001</v>
@@ -15274,7 +15271,7 @@
         <v>658</v>
       </c>
       <c r="I295" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="J295">
         <v>64.62</v>
@@ -15690,7 +15687,7 @@
         <v>638</v>
       </c>
       <c r="I305" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J305">
         <v>13.56</v>
@@ -15860,7 +15857,7 @@
         <v>594</v>
       </c>
       <c r="I309" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J309">
         <v>9.82</v>
@@ -15907,7 +15904,7 @@
         <v>659</v>
       </c>
       <c r="I310" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J310">
         <v>10.19</v>
@@ -16036,7 +16033,7 @@
         <v>610</v>
       </c>
       <c r="I313" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J313">
         <v>32.05</v>
@@ -16124,7 +16121,7 @@
         <v>660</v>
       </c>
       <c r="I315" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="J315">
         <v>9.44</v>
@@ -16171,7 +16168,7 @@
         <v>594</v>
       </c>
       <c r="I316" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J316">
         <v>27.99</v>
@@ -16218,7 +16215,7 @@
         <v>646</v>
       </c>
       <c r="I317" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J317">
         <v>13.03</v>
@@ -16265,7 +16262,7 @@
         <v>661</v>
       </c>
       <c r="I318" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J318">
         <v>61.82</v>
@@ -16312,7 +16309,7 @@
         <v>606</v>
       </c>
       <c r="I319" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J319">
         <v>19.09</v>
@@ -16564,7 +16561,7 @@
         <v>662</v>
       </c>
       <c r="I325" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J325">
         <v>6.42</v>
@@ -16693,7 +16690,7 @@
         <v>594</v>
       </c>
       <c r="I328" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J328">
         <v>37.76</v>
@@ -16740,7 +16737,7 @@
         <v>638</v>
       </c>
       <c r="I329" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J329">
         <v>110.35</v>
@@ -16869,7 +16866,7 @@
         <v>600</v>
       </c>
       <c r="I332" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J332">
         <v>21.08</v>
@@ -16957,7 +16954,7 @@
         <v>610</v>
       </c>
       <c r="I334" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J334">
         <v>10.28</v>
@@ -17045,7 +17042,7 @@
         <v>618</v>
       </c>
       <c r="I336" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J336">
         <v>3.03</v>
@@ -17133,7 +17130,7 @@
         <v>663</v>
       </c>
       <c r="I338" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J338">
         <v>135.4</v>
@@ -17262,7 +17259,7 @@
         <v>664</v>
       </c>
       <c r="I341" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J341">
         <v>77.06999999999999</v>
@@ -17391,7 +17388,7 @@
         <v>665</v>
       </c>
       <c r="I344" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J344">
         <v>107.54</v>
@@ -17766,7 +17763,7 @@
         <v>666</v>
       </c>
       <c r="I353" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J353">
         <v>189.77</v>
@@ -17813,7 +17810,7 @@
         <v>594</v>
       </c>
       <c r="I354" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J354">
         <v>15625.35</v>
@@ -18024,7 +18021,7 @@
         <v>667</v>
       </c>
       <c r="I359" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J359">
         <v>28.68</v>
@@ -18153,7 +18150,7 @@
         <v>618</v>
       </c>
       <c r="I362" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J362">
         <v>2.73</v>
@@ -18200,7 +18197,7 @@
         <v>638</v>
       </c>
       <c r="I363" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J363">
         <v>1.89</v>
@@ -18288,7 +18285,7 @@
         <v>618</v>
       </c>
       <c r="I365" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J365">
         <v>180.16</v>
@@ -18417,7 +18414,7 @@
         <v>668</v>
       </c>
       <c r="I368" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J368">
         <v>80.18000000000001</v>
@@ -18505,7 +18502,7 @@
         <v>603</v>
       </c>
       <c r="I370" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J370">
         <v>25.29</v>
@@ -18552,7 +18549,7 @@
         <v>659</v>
       </c>
       <c r="I371" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J371">
         <v>24.35</v>
@@ -18722,7 +18719,7 @@
         <v>594</v>
       </c>
       <c r="I375" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J375">
         <v>661.27</v>
@@ -18769,7 +18766,7 @@
         <v>603</v>
       </c>
       <c r="I376" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J376">
         <v>4.02</v>
@@ -18816,7 +18813,7 @@
         <v>610</v>
       </c>
       <c r="I377" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J377">
         <v>43.56</v>
@@ -18904,7 +18901,7 @@
         <v>594</v>
       </c>
       <c r="I379" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J379">
         <v>11.66</v>
@@ -18951,7 +18948,7 @@
         <v>594</v>
       </c>
       <c r="I380" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J380">
         <v>5.99</v>
@@ -18998,7 +18995,7 @@
         <v>669</v>
       </c>
       <c r="I381" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J381">
         <v>12.85</v>
@@ -19086,7 +19083,7 @@
         <v>670</v>
       </c>
       <c r="I383" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J383">
         <v>38.82</v>
@@ -19174,7 +19171,7 @@
         <v>618</v>
       </c>
       <c r="I385" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J385">
         <v>1.62</v>
@@ -19303,7 +19300,7 @@
         <v>603</v>
       </c>
       <c r="I388" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J388">
         <v>25.29</v>
@@ -19473,7 +19470,7 @@
         <v>600</v>
       </c>
       <c r="I392" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J392">
         <v>67.45999999999999</v>
@@ -19561,7 +19558,7 @@
         <v>594</v>
       </c>
       <c r="I394" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J394">
         <v>12.52</v>
@@ -19649,7 +19646,7 @@
         <v>610</v>
       </c>
       <c r="I396" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J396">
         <v>9.890000000000001</v>
@@ -19737,7 +19734,7 @@
         <v>594</v>
       </c>
       <c r="I398" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J398">
         <v>7.74</v>
@@ -19825,7 +19822,7 @@
         <v>605</v>
       </c>
       <c r="I400" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J400">
         <v>8.029999999999999</v>
@@ -20241,7 +20238,7 @@
         <v>605</v>
       </c>
       <c r="I410" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J410">
         <v>250.2</v>
@@ -20288,7 +20285,7 @@
         <v>597</v>
       </c>
       <c r="I411" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J411">
         <v>23.56</v>
@@ -20499,7 +20496,7 @@
         <v>671</v>
       </c>
       <c r="I416" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J416">
         <v>2.27</v>
@@ -20587,7 +20584,7 @@
         <v>618</v>
       </c>
       <c r="I418" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J418">
         <v>31.75</v>
@@ -20634,7 +20631,7 @@
         <v>672</v>
       </c>
       <c r="I419" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="J419">
         <v>30.68</v>
@@ -20722,7 +20719,7 @@
         <v>595</v>
       </c>
       <c r="I421" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J421">
         <v>138.29</v>
@@ -21015,7 +21012,7 @@
         <v>673</v>
       </c>
       <c r="I428" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J428">
         <v>31</v>
@@ -21103,7 +21100,7 @@
         <v>594</v>
       </c>
       <c r="I430" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J430">
         <v>11.91</v>
@@ -21314,7 +21311,7 @@
         <v>599</v>
       </c>
       <c r="I435" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J435">
         <v>11.56</v>
@@ -21361,7 +21358,7 @@
         <v>622</v>
       </c>
       <c r="I436" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J436">
         <v>130.11</v>
@@ -21572,7 +21569,7 @@
         <v>605</v>
       </c>
       <c r="I441" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J441">
         <v>21.17</v>
@@ -21660,7 +21657,7 @@
         <v>674</v>
       </c>
       <c r="I443" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J443">
         <v>7.59</v>
@@ -21912,7 +21909,7 @@
         <v>675</v>
       </c>
       <c r="I449" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J449">
         <v>45.97</v>
@@ -22000,7 +21997,7 @@
         <v>676</v>
       </c>
       <c r="I451" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J451">
         <v>3.89</v>
@@ -22334,7 +22331,7 @@
         <v>630</v>
       </c>
       <c r="I459" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J459">
         <v>28.07</v>
@@ -22381,7 +22378,7 @@
         <v>594</v>
       </c>
       <c r="I460" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J460">
         <v>11.78</v>
@@ -22428,7 +22425,7 @@
         <v>677</v>
       </c>
       <c r="I461" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J461">
         <v>31.92</v>
@@ -22762,7 +22759,7 @@
         <v>594</v>
       </c>
       <c r="I469" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J469">
         <v>34.2</v>
@@ -22809,7 +22806,7 @@
         <v>650</v>
       </c>
       <c r="I470" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J470">
         <v>2.81</v>
@@ -22856,7 +22853,7 @@
         <v>594</v>
       </c>
       <c r="I471" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J471">
         <v>52.9</v>
@@ -22903,7 +22900,7 @@
         <v>611</v>
       </c>
       <c r="I472" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J472">
         <v>243.33</v>
@@ -23073,7 +23070,7 @@
         <v>678</v>
       </c>
       <c r="I476" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J476">
         <v>8.85</v>
@@ -23120,7 +23117,7 @@
         <v>617</v>
       </c>
       <c r="I477" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J477">
         <v>163.46</v>
@@ -23167,7 +23164,7 @@
         <v>630</v>
       </c>
       <c r="I478" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J478">
         <v>2.38</v>
@@ -23337,7 +23334,7 @@
         <v>603</v>
       </c>
       <c r="I482" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="J482">
         <v>46.49</v>
@@ -23507,7 +23504,7 @@
         <v>641</v>
       </c>
       <c r="I486" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J486">
         <v>14.23</v>
@@ -23554,7 +23551,7 @@
         <v>594</v>
       </c>
       <c r="I487" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J487">
         <v>34.27</v>
@@ -23601,7 +23598,7 @@
         <v>600</v>
       </c>
       <c r="I488" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J488">
         <v>10.68</v>
@@ -23812,7 +23809,7 @@
         <v>679</v>
       </c>
       <c r="I493" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="J493">
         <v>17.47</v>
@@ -23882,43 +23879,37 @@
         <v>593</v>
       </c>
       <c r="C495">
-        <v>125</v>
+        <v>2.6</v>
       </c>
       <c r="D495">
-        <v>1.13</v>
+        <v>-0.38</v>
       </c>
       <c r="E495">
-        <v>50.56</v>
+        <v>12.78</v>
       </c>
       <c r="F495">
-        <v>44.54</v>
+        <v>31.1</v>
       </c>
       <c r="G495">
-        <v>-0.26</v>
-      </c>
-      <c r="H495" t="s">
-        <v>680</v>
-      </c>
-      <c r="I495" t="s">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="J495">
-        <v>129.15</v>
+        <v>3.02</v>
       </c>
       <c r="K495">
-        <v>128.47</v>
+        <v>2.89</v>
       </c>
       <c r="L495">
-        <v>128.88</v>
+        <v>2.62</v>
       </c>
       <c r="M495">
-        <v>129.06</v>
+        <v>2.93</v>
       </c>
       <c r="N495">
-        <v>128.15</v>
+        <v>2.64</v>
       </c>
       <c r="O495">
-        <v>128.74</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="496" spans="1:15">
@@ -23929,37 +23920,37 @@
         <v>593</v>
       </c>
       <c r="C496">
-        <v>2.6</v>
+        <v>335</v>
       </c>
       <c r="D496">
-        <v>-0.38</v>
+        <v>-1.33</v>
       </c>
       <c r="E496">
-        <v>12.78</v>
+        <v>-29.75</v>
       </c>
       <c r="F496">
-        <v>31.1</v>
+        <v>46.49</v>
       </c>
       <c r="G496">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="J496">
-        <v>3.02</v>
+        <v>343.29</v>
       </c>
       <c r="K496">
-        <v>2.89</v>
+        <v>377.22</v>
       </c>
       <c r="L496">
-        <v>2.62</v>
+        <v>366.43</v>
       </c>
       <c r="M496">
-        <v>2.93</v>
+        <v>350.94</v>
       </c>
       <c r="N496">
-        <v>2.64</v>
+        <v>371.04</v>
       </c>
       <c r="O496">
-        <v>2.6</v>
+        <v>328.74</v>
       </c>
     </row>
     <row r="497" spans="1:15">
@@ -23970,37 +23961,37 @@
         <v>593</v>
       </c>
       <c r="C497">
-        <v>335</v>
+        <v>41.98</v>
       </c>
       <c r="D497">
-        <v>-1.33</v>
+        <v>2.69</v>
       </c>
       <c r="E497">
-        <v>-29.75</v>
+        <v>-40.12</v>
       </c>
       <c r="F497">
-        <v>46.49</v>
+        <v>64.14</v>
       </c>
       <c r="G497">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="J497">
-        <v>343.29</v>
+        <v>36.81</v>
       </c>
       <c r="K497">
-        <v>377.22</v>
+        <v>36.32</v>
       </c>
       <c r="L497">
-        <v>366.43</v>
+        <v>36.49</v>
       </c>
       <c r="M497">
-        <v>350.94</v>
+        <v>36.3</v>
       </c>
       <c r="N497">
-        <v>371.04</v>
+        <v>36.38</v>
       </c>
       <c r="O497">
-        <v>328.74</v>
+        <v>38.41</v>
       </c>
     </row>
     <row r="498" spans="1:15">
@@ -24011,37 +24002,43 @@
         <v>593</v>
       </c>
       <c r="C498">
-        <v>41.98</v>
+        <v>68.5</v>
       </c>
       <c r="D498">
-        <v>2.69</v>
+        <v>-2.14</v>
       </c>
       <c r="E498">
-        <v>-40.12</v>
+        <v>-25.73</v>
       </c>
       <c r="F498">
-        <v>64.14</v>
+        <v>45.73</v>
       </c>
       <c r="G498">
-        <v>1.16</v>
+        <v>0.06</v>
+      </c>
+      <c r="H498" t="s">
+        <v>659</v>
+      </c>
+      <c r="I498" t="s">
+        <v>686</v>
       </c>
       <c r="J498">
-        <v>36.81</v>
+        <v>69.06</v>
       </c>
       <c r="K498">
-        <v>36.32</v>
+        <v>71.81</v>
       </c>
       <c r="L498">
-        <v>36.49</v>
+        <v>71.66</v>
       </c>
       <c r="M498">
-        <v>36.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="N498">
-        <v>36.38</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="O498">
-        <v>38.41</v>
+        <v>69.94</v>
       </c>
     </row>
     <row r="499" spans="1:15">
@@ -24052,43 +24049,43 @@
         <v>593</v>
       </c>
       <c r="C499">
-        <v>68.5</v>
+        <v>7.06</v>
       </c>
       <c r="D499">
-        <v>-2.14</v>
+        <v>-1.53</v>
       </c>
       <c r="E499">
-        <v>-25.73</v>
+        <v>-42.96</v>
       </c>
       <c r="F499">
-        <v>45.73</v>
+        <v>48.92</v>
       </c>
       <c r="G499">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="H499" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
       <c r="I499" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="J499">
-        <v>69.06</v>
+        <v>7.87</v>
       </c>
       <c r="K499">
-        <v>71.81</v>
+        <v>7.21</v>
       </c>
       <c r="L499">
-        <v>71.66</v>
+        <v>7.07</v>
       </c>
       <c r="M499">
-        <v>70.59999999999999</v>
+        <v>7.26</v>
       </c>
       <c r="N499">
-        <v>70.90000000000001</v>
+        <v>7.15</v>
       </c>
       <c r="O499">
-        <v>69.94</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="500" spans="1:15">
@@ -24099,43 +24096,43 @@
         <v>593</v>
       </c>
       <c r="C500">
-        <v>7.06</v>
+        <v>233</v>
       </c>
       <c r="D500">
-        <v>-1.53</v>
+        <v>0</v>
       </c>
       <c r="E500">
-        <v>-42.96</v>
+        <v>-7.59</v>
       </c>
       <c r="F500">
-        <v>48.92</v>
+        <v>45.84</v>
       </c>
       <c r="G500">
-        <v>0.11</v>
+        <v>1.95</v>
       </c>
       <c r="H500" t="s">
-        <v>643</v>
+        <v>603</v>
       </c>
       <c r="I500" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="J500">
-        <v>7.87</v>
+        <v>248.04</v>
       </c>
       <c r="K500">
-        <v>7.21</v>
+        <v>242.55</v>
       </c>
       <c r="L500">
-        <v>7.07</v>
+        <v>236.86</v>
       </c>
       <c r="M500">
-        <v>7.26</v>
+        <v>246.38</v>
       </c>
       <c r="N500">
-        <v>7.15</v>
+        <v>239.97</v>
       </c>
       <c r="O500">
-        <v>7.1</v>
+        <v>231.78</v>
       </c>
     </row>
     <row r="501" spans="1:15">
@@ -24146,43 +24143,43 @@
         <v>593</v>
       </c>
       <c r="C501">
-        <v>233</v>
+        <v>13.12</v>
       </c>
       <c r="D501">
-        <v>0</v>
+        <v>-4.79</v>
       </c>
       <c r="E501">
-        <v>-7.59</v>
+        <v>-34.4</v>
       </c>
       <c r="F501">
-        <v>45.84</v>
+        <v>48.73</v>
       </c>
       <c r="G501">
-        <v>1.95</v>
+        <v>0.2</v>
       </c>
       <c r="H501" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="I501" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="J501">
-        <v>248.04</v>
+        <v>15.22</v>
       </c>
       <c r="K501">
-        <v>242.55</v>
+        <v>15.29</v>
       </c>
       <c r="L501">
-        <v>236.86</v>
+        <v>13.2</v>
       </c>
       <c r="M501">
-        <v>246.38</v>
+        <v>15.54</v>
       </c>
       <c r="N501">
-        <v>239.97</v>
+        <v>13.67</v>
       </c>
       <c r="O501">
-        <v>231.78</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="502" spans="1:15">
@@ -24193,43 +24190,43 @@
         <v>593</v>
       </c>
       <c r="C502">
-        <v>13.12</v>
+        <v>19.51</v>
       </c>
       <c r="D502">
-        <v>-4.79</v>
+        <v>-1.27</v>
       </c>
       <c r="E502">
-        <v>-34.4</v>
+        <v>122.54</v>
       </c>
       <c r="F502">
-        <v>48.73</v>
+        <v>52.56</v>
       </c>
       <c r="G502">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="H502" t="s">
-        <v>599</v>
+        <v>636</v>
       </c>
       <c r="I502" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J502">
-        <v>15.22</v>
+        <v>19.02</v>
       </c>
       <c r="K502">
-        <v>15.29</v>
+        <v>19.62</v>
       </c>
       <c r="L502">
-        <v>13.2</v>
+        <v>19.28</v>
       </c>
       <c r="M502">
-        <v>15.54</v>
+        <v>19.3</v>
       </c>
       <c r="N502">
-        <v>13.67</v>
+        <v>19.3</v>
       </c>
       <c r="O502">
-        <v>12.74</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="503" spans="1:15">
@@ -24240,43 +24237,37 @@
         <v>593</v>
       </c>
       <c r="C503">
-        <v>19.51</v>
+        <v>259.5</v>
       </c>
       <c r="D503">
-        <v>-1.27</v>
+        <v>0.1</v>
       </c>
       <c r="E503">
-        <v>122.54</v>
+        <v>3.35</v>
       </c>
       <c r="F503">
-        <v>52.56</v>
+        <v>41.27</v>
       </c>
       <c r="G503">
-        <v>0.13</v>
-      </c>
-      <c r="H503" t="s">
-        <v>636</v>
-      </c>
-      <c r="I503" t="s">
-        <v>687</v>
+        <v>-0.72</v>
       </c>
       <c r="J503">
-        <v>19.02</v>
+        <v>298.38</v>
       </c>
       <c r="K503">
-        <v>19.62</v>
+        <v>280.68</v>
       </c>
       <c r="L503">
-        <v>19.28</v>
+        <v>279.82</v>
       </c>
       <c r="M503">
-        <v>19.3</v>
+        <v>284.79</v>
       </c>
       <c r="N503">
-        <v>19.3</v>
+        <v>273.72</v>
       </c>
       <c r="O503">
-        <v>19.31</v>
+        <v>266.47</v>
       </c>
     </row>
     <row r="504" spans="1:15">
@@ -24287,37 +24278,37 @@
         <v>593</v>
       </c>
       <c r="C504">
-        <v>259.5</v>
+        <v>129.6</v>
       </c>
       <c r="D504">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="E504">
-        <v>3.35</v>
+        <v>1.64</v>
       </c>
       <c r="F504">
-        <v>41.27</v>
+        <v>46.94</v>
       </c>
       <c r="G504">
-        <v>-0.72</v>
+        <v>0.33</v>
       </c>
       <c r="J504">
-        <v>298.38</v>
+        <v>134.5</v>
       </c>
       <c r="K504">
-        <v>280.68</v>
+        <v>131.24</v>
       </c>
       <c r="L504">
-        <v>279.82</v>
+        <v>129.74</v>
       </c>
       <c r="M504">
-        <v>284.79</v>
+        <v>132.79</v>
       </c>
       <c r="N504">
-        <v>273.72</v>
+        <v>129.81</v>
       </c>
       <c r="O504">
-        <v>266.47</v>
+        <v>127.35</v>
       </c>
     </row>
     <row r="505" spans="1:15">
@@ -24328,37 +24319,37 @@
         <v>593</v>
       </c>
       <c r="C505">
-        <v>129.6</v>
+        <v>103.7</v>
       </c>
       <c r="D505">
-        <v>0.7</v>
+        <v>-1.24</v>
       </c>
       <c r="E505">
-        <v>1.64</v>
+        <v>-22.75</v>
       </c>
       <c r="F505">
-        <v>46.94</v>
+        <v>39.87</v>
       </c>
       <c r="G505">
-        <v>0.33</v>
+        <v>-0.3</v>
       </c>
       <c r="J505">
-        <v>134.5</v>
+        <v>108.86</v>
       </c>
       <c r="K505">
-        <v>131.24</v>
+        <v>109.31</v>
       </c>
       <c r="L505">
-        <v>129.74</v>
+        <v>108.16</v>
       </c>
       <c r="M505">
-        <v>132.79</v>
+        <v>109.58</v>
       </c>
       <c r="N505">
-        <v>129.81</v>
+        <v>108.23</v>
       </c>
       <c r="O505">
-        <v>127.35</v>
+        <v>107.91</v>
       </c>
     </row>
     <row r="506" spans="1:15">
@@ -24369,37 +24360,43 @@
         <v>593</v>
       </c>
       <c r="C506">
-        <v>103.7</v>
+        <v>140.3</v>
       </c>
       <c r="D506">
-        <v>-1.24</v>
+        <v>0.86</v>
       </c>
       <c r="E506">
-        <v>-22.75</v>
+        <v>-36.66</v>
       </c>
       <c r="F506">
-        <v>39.87</v>
+        <v>52.73</v>
       </c>
       <c r="G506">
-        <v>-0.3</v>
+        <v>1</v>
+      </c>
+      <c r="H506" t="s">
+        <v>678</v>
+      </c>
+      <c r="I506" t="s">
+        <v>688</v>
       </c>
       <c r="J506">
-        <v>108.86</v>
+        <v>125.85</v>
       </c>
       <c r="K506">
-        <v>109.31</v>
+        <v>142.07</v>
       </c>
       <c r="L506">
-        <v>108.16</v>
+        <v>132.88</v>
       </c>
       <c r="M506">
-        <v>109.58</v>
+        <v>128.61</v>
       </c>
       <c r="N506">
-        <v>108.23</v>
+        <v>139.44</v>
       </c>
       <c r="O506">
-        <v>107.91</v>
+        <v>128.02</v>
       </c>
     </row>
     <row r="507" spans="1:15">
@@ -24410,43 +24407,43 @@
         <v>593</v>
       </c>
       <c r="C507">
-        <v>140.3</v>
+        <v>16.16</v>
       </c>
       <c r="D507">
-        <v>0.86</v>
+        <v>-0.06</v>
       </c>
       <c r="E507">
-        <v>-36.66</v>
+        <v>-12.15</v>
       </c>
       <c r="F507">
-        <v>52.73</v>
+        <v>54.8</v>
       </c>
       <c r="G507">
-        <v>1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H507" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="I507" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="J507">
-        <v>125.85</v>
+        <v>20.36</v>
       </c>
       <c r="K507">
-        <v>142.07</v>
+        <v>16.32</v>
       </c>
       <c r="L507">
-        <v>132.88</v>
+        <v>15.54</v>
       </c>
       <c r="M507">
-        <v>128.61</v>
+        <v>16.72</v>
       </c>
       <c r="N507">
-        <v>139.44</v>
+        <v>15.7</v>
       </c>
       <c r="O507">
-        <v>128.02</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="508" spans="1:15">
@@ -24457,43 +24454,37 @@
         <v>593</v>
       </c>
       <c r="C508">
-        <v>16.16</v>
+        <v>43.1</v>
       </c>
       <c r="D508">
-        <v>-0.06</v>
+        <v>0.19</v>
       </c>
       <c r="E508">
-        <v>-12.15</v>
+        <v>-59.95</v>
       </c>
       <c r="F508">
-        <v>54.8</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="G508">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H508" t="s">
-        <v>667</v>
-      </c>
-      <c r="I508" t="s">
-        <v>692</v>
+        <v>-0.05</v>
       </c>
       <c r="J508">
-        <v>20.36</v>
+        <v>31.35</v>
       </c>
       <c r="K508">
-        <v>16.32</v>
+        <v>33.27</v>
       </c>
       <c r="L508">
-        <v>15.54</v>
+        <v>41.99</v>
       </c>
       <c r="M508">
-        <v>16.72</v>
+        <v>22.75</v>
       </c>
       <c r="N508">
-        <v>15.7</v>
+        <v>32.37</v>
       </c>
       <c r="O508">
-        <v>15.58</v>
+        <v>34.31</v>
       </c>
     </row>
     <row r="509" spans="1:15">
@@ -24504,37 +24495,37 @@
         <v>593</v>
       </c>
       <c r="C509">
-        <v>43.1</v>
+        <v>8.19</v>
       </c>
       <c r="D509">
-        <v>0.19</v>
+        <v>-2.5</v>
       </c>
       <c r="E509">
-        <v>-59.95</v>
+        <v>29.48</v>
       </c>
       <c r="F509">
-        <v>90.70999999999999</v>
+        <v>33.36</v>
       </c>
       <c r="G509">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="J509">
-        <v>31.35</v>
+        <v>10.37</v>
       </c>
       <c r="K509">
-        <v>33.27</v>
+        <v>9.52</v>
       </c>
       <c r="L509">
-        <v>41.99</v>
+        <v>9.16</v>
       </c>
       <c r="M509">
-        <v>22.75</v>
+        <v>10.63</v>
       </c>
       <c r="N509">
-        <v>32.37</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="O509">
-        <v>34.31</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="510" spans="1:15">
@@ -24545,37 +24536,37 @@
         <v>593</v>
       </c>
       <c r="C510">
-        <v>8.19</v>
+        <v>164.4</v>
       </c>
       <c r="D510">
-        <v>-2.5</v>
+        <v>2.11</v>
       </c>
       <c r="E510">
-        <v>29.48</v>
+        <v>-20.72</v>
       </c>
       <c r="F510">
-        <v>33.36</v>
+        <v>46.18</v>
       </c>
       <c r="G510">
-        <v>-0.09</v>
+        <v>3.11</v>
       </c>
       <c r="J510">
-        <v>10.37</v>
+        <v>200.71</v>
       </c>
       <c r="K510">
-        <v>9.52</v>
+        <v>182.35</v>
       </c>
       <c r="L510">
-        <v>9.16</v>
+        <v>167.59</v>
       </c>
       <c r="M510">
-        <v>10.63</v>
+        <v>200</v>
       </c>
       <c r="N510">
-        <v>9.960000000000001</v>
+        <v>174.32</v>
       </c>
       <c r="O510">
-        <v>9.34</v>
+        <v>160.73</v>
       </c>
     </row>
     <row r="511" spans="1:15">
@@ -24586,37 +24577,37 @@
         <v>593</v>
       </c>
       <c r="C511">
-        <v>164.4</v>
+        <v>13.69</v>
       </c>
       <c r="D511">
-        <v>2.11</v>
+        <v>-4.8</v>
       </c>
       <c r="E511">
-        <v>-20.72</v>
+        <v>-49.28</v>
       </c>
       <c r="F511">
-        <v>46.18</v>
+        <v>21.75</v>
       </c>
       <c r="G511">
-        <v>3.11</v>
+        <v>-0.13</v>
       </c>
       <c r="J511">
-        <v>200.71</v>
+        <v>17.8</v>
       </c>
       <c r="K511">
-        <v>182.35</v>
+        <v>17.02</v>
       </c>
       <c r="L511">
-        <v>167.59</v>
+        <v>15.25</v>
       </c>
       <c r="M511">
-        <v>200</v>
+        <v>17.96</v>
       </c>
       <c r="N511">
-        <v>174.32</v>
+        <v>17.46</v>
       </c>
       <c r="O511">
-        <v>160.73</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="512" spans="1:15">
@@ -24627,37 +24618,43 @@
         <v>593</v>
       </c>
       <c r="C512">
-        <v>13.69</v>
+        <v>181</v>
       </c>
       <c r="D512">
-        <v>-4.8</v>
+        <v>0.22</v>
       </c>
       <c r="E512">
-        <v>-49.28</v>
+        <v>-63.69</v>
       </c>
       <c r="F512">
-        <v>21.75</v>
+        <v>51.84</v>
       </c>
       <c r="G512">
-        <v>-0.13</v>
+        <v>0.05</v>
+      </c>
+      <c r="H512" t="s">
+        <v>680</v>
+      </c>
+      <c r="I512" t="s">
+        <v>688</v>
       </c>
       <c r="J512">
-        <v>17.8</v>
+        <v>179.94</v>
       </c>
       <c r="K512">
-        <v>17.02</v>
+        <v>179.41</v>
       </c>
       <c r="L512">
-        <v>15.25</v>
+        <v>181.4</v>
       </c>
       <c r="M512">
-        <v>17.96</v>
+        <v>179.08</v>
       </c>
       <c r="N512">
-        <v>17.46</v>
+        <v>180.79</v>
       </c>
       <c r="O512">
-        <v>15.55</v>
+        <v>181.99</v>
       </c>
     </row>
     <row r="513" spans="1:15">
@@ -24668,43 +24665,37 @@
         <v>593</v>
       </c>
       <c r="C513">
-        <v>181</v>
+        <v>312</v>
       </c>
       <c r="D513">
-        <v>0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="E513">
-        <v>-63.69</v>
+        <v>-58.33</v>
       </c>
       <c r="F513">
-        <v>51.84</v>
+        <v>40.85</v>
       </c>
       <c r="G513">
-        <v>0.05</v>
-      </c>
-      <c r="H513" t="s">
-        <v>681</v>
-      </c>
-      <c r="I513" t="s">
-        <v>689</v>
+        <v>-3.67</v>
       </c>
       <c r="J513">
-        <v>179.94</v>
+        <v>312.78</v>
       </c>
       <c r="K513">
-        <v>179.41</v>
+        <v>317.64</v>
       </c>
       <c r="L513">
-        <v>181.4</v>
+        <v>329.77</v>
       </c>
       <c r="M513">
-        <v>179.08</v>
+        <v>310.26</v>
       </c>
       <c r="N513">
-        <v>180.79</v>
+        <v>313.17</v>
       </c>
       <c r="O513">
-        <v>181.99</v>
+        <v>321.08</v>
       </c>
     </row>
     <row r="514" spans="1:15">
@@ -24715,37 +24706,37 @@
         <v>593</v>
       </c>
       <c r="C514">
-        <v>312</v>
+        <v>150</v>
       </c>
       <c r="D514">
-        <v>-0.24</v>
+        <v>2.81</v>
       </c>
       <c r="E514">
-        <v>-58.33</v>
+        <v>-17.72</v>
       </c>
       <c r="F514">
-        <v>40.85</v>
+        <v>63.37</v>
       </c>
       <c r="G514">
-        <v>-3.67</v>
+        <v>1.17</v>
       </c>
       <c r="J514">
-        <v>312.78</v>
+        <v>114.78</v>
       </c>
       <c r="K514">
-        <v>317.64</v>
+        <v>140.34</v>
       </c>
       <c r="L514">
-        <v>329.77</v>
+        <v>140.67</v>
       </c>
       <c r="M514">
-        <v>310.26</v>
+        <v>120.65</v>
       </c>
       <c r="N514">
-        <v>313.17</v>
+        <v>140.1</v>
       </c>
       <c r="O514">
-        <v>321.08</v>
+        <v>142.53</v>
       </c>
     </row>
     <row r="515" spans="1:15">
@@ -24756,37 +24747,37 @@
         <v>593</v>
       </c>
       <c r="C515">
-        <v>150</v>
+        <v>17.5</v>
       </c>
       <c r="D515">
-        <v>2.81</v>
+        <v>-1.57</v>
       </c>
       <c r="E515">
-        <v>-17.72</v>
+        <v>-47.23</v>
       </c>
       <c r="F515">
-        <v>63.37</v>
+        <v>25.86</v>
       </c>
       <c r="G515">
-        <v>1.17</v>
+        <v>-0.06</v>
       </c>
       <c r="J515">
-        <v>114.78</v>
+        <v>22.41</v>
       </c>
       <c r="K515">
-        <v>140.34</v>
+        <v>21.49</v>
       </c>
       <c r="L515">
-        <v>140.67</v>
+        <v>19.12</v>
       </c>
       <c r="M515">
-        <v>120.65</v>
+        <v>22.61</v>
       </c>
       <c r="N515">
-        <v>140.1</v>
+        <v>22.11</v>
       </c>
       <c r="O515">
-        <v>142.53</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="516" spans="1:15">
@@ -24797,37 +24788,37 @@
         <v>593</v>
       </c>
       <c r="C516">
-        <v>17.5</v>
+        <v>85.05</v>
       </c>
       <c r="D516">
-        <v>-1.57</v>
+        <v>0.12</v>
       </c>
       <c r="E516">
-        <v>-47.23</v>
+        <v>-40.82</v>
       </c>
       <c r="F516">
-        <v>25.86</v>
+        <v>31.6</v>
       </c>
       <c r="G516">
         <v>-0.06</v>
       </c>
       <c r="J516">
-        <v>22.41</v>
+        <v>95.87</v>
       </c>
       <c r="K516">
-        <v>21.49</v>
+        <v>94.92</v>
       </c>
       <c r="L516">
-        <v>19.12</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="M516">
-        <v>22.61</v>
+        <v>95.97</v>
       </c>
       <c r="N516">
-        <v>22.11</v>
+        <v>96.03</v>
       </c>
       <c r="O516">
-        <v>19.71</v>
+        <v>92.51000000000001</v>
       </c>
     </row>
     <row r="517" spans="1:15">
@@ -24838,37 +24829,43 @@
         <v>593</v>
       </c>
       <c r="C517">
-        <v>85.05</v>
+        <v>426.5</v>
       </c>
       <c r="D517">
-        <v>0.12</v>
+        <v>-1.78</v>
       </c>
       <c r="E517">
-        <v>-40.82</v>
+        <v>-20.05</v>
       </c>
       <c r="F517">
-        <v>31.6</v>
+        <v>45.75</v>
       </c>
       <c r="G517">
-        <v>-0.06</v>
+        <v>-2.74</v>
+      </c>
+      <c r="H517" t="s">
+        <v>669</v>
+      </c>
+      <c r="I517" t="s">
+        <v>686</v>
       </c>
       <c r="J517">
-        <v>95.87</v>
+        <v>447.28</v>
       </c>
       <c r="K517">
-        <v>94.92</v>
+        <v>420.88</v>
       </c>
       <c r="L517">
-        <v>91.45999999999999</v>
+        <v>442.19</v>
       </c>
       <c r="M517">
-        <v>95.97</v>
+        <v>460.27</v>
       </c>
       <c r="N517">
-        <v>96.03</v>
+        <v>431.96</v>
       </c>
       <c r="O517">
-        <v>92.51000000000001</v>
+        <v>414.75</v>
       </c>
     </row>
     <row r="518" spans="1:15">
@@ -24879,43 +24876,43 @@
         <v>593</v>
       </c>
       <c r="C518">
-        <v>426.5</v>
+        <v>83.2</v>
       </c>
       <c r="D518">
-        <v>-1.78</v>
+        <v>3.61</v>
       </c>
       <c r="E518">
-        <v>-20.05</v>
+        <v>762.53</v>
       </c>
       <c r="F518">
-        <v>45.75</v>
+        <v>40.69</v>
       </c>
       <c r="G518">
-        <v>-2.74</v>
+        <v>0.05</v>
       </c>
       <c r="H518" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="I518" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J518">
-        <v>447.28</v>
+        <v>92.41</v>
       </c>
       <c r="K518">
-        <v>420.88</v>
+        <v>85.63</v>
       </c>
       <c r="L518">
-        <v>442.19</v>
+        <v>83.94</v>
       </c>
       <c r="M518">
-        <v>460.27</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="N518">
-        <v>431.96</v>
+        <v>84.94</v>
       </c>
       <c r="O518">
-        <v>414.75</v>
+        <v>82.95</v>
       </c>
     </row>
     <row r="519" spans="1:15">
@@ -24926,43 +24923,37 @@
         <v>593</v>
       </c>
       <c r="C519">
-        <v>83.2</v>
+        <v>25.02</v>
       </c>
       <c r="D519">
-        <v>3.61</v>
+        <v>0.16</v>
       </c>
       <c r="E519">
-        <v>762.53</v>
+        <v>-13.09</v>
       </c>
       <c r="F519">
-        <v>40.69</v>
+        <v>54.33</v>
       </c>
       <c r="G519">
-        <v>0.05</v>
-      </c>
-      <c r="H519" t="s">
-        <v>682</v>
-      </c>
-      <c r="I519" t="s">
-        <v>689</v>
+        <v>0.18</v>
       </c>
       <c r="J519">
-        <v>92.41</v>
+        <v>24.7</v>
       </c>
       <c r="K519">
-        <v>85.63</v>
+        <v>25.69</v>
       </c>
       <c r="L519">
-        <v>83.94</v>
+        <v>25.06</v>
       </c>
       <c r="M519">
-        <v>87.34999999999999</v>
+        <v>24.77</v>
       </c>
       <c r="N519">
-        <v>84.94</v>
+        <v>25.16</v>
       </c>
       <c r="O519">
-        <v>82.95</v>
+        <v>24.11</v>
       </c>
     </row>
     <row r="520" spans="1:15">
@@ -24973,37 +24964,37 @@
         <v>593</v>
       </c>
       <c r="C520">
-        <v>25.02</v>
+        <v>281</v>
       </c>
       <c r="D520">
-        <v>0.16</v>
+        <v>-1.83</v>
       </c>
       <c r="E520">
-        <v>-13.09</v>
+        <v>-1.04</v>
       </c>
       <c r="F520">
-        <v>54.33</v>
+        <v>34.69</v>
       </c>
       <c r="G520">
-        <v>0.18</v>
+        <v>-2.26</v>
       </c>
       <c r="J520">
-        <v>24.7</v>
+        <v>299.14</v>
       </c>
       <c r="K520">
-        <v>25.69</v>
+        <v>307.89</v>
       </c>
       <c r="L520">
-        <v>25.06</v>
+        <v>306.68</v>
       </c>
       <c r="M520">
-        <v>24.77</v>
+        <v>299.56</v>
       </c>
       <c r="N520">
-        <v>25.16</v>
+        <v>302.56</v>
       </c>
       <c r="O520">
-        <v>24.11</v>
+        <v>308.61</v>
       </c>
     </row>
     <row r="521" spans="1:15">
@@ -25014,37 +25005,43 @@
         <v>593</v>
       </c>
       <c r="C521">
-        <v>281</v>
+        <v>49.12</v>
       </c>
       <c r="D521">
-        <v>-1.83</v>
+        <v>-2.83</v>
       </c>
       <c r="E521">
-        <v>-1.04</v>
+        <v>-28.53</v>
       </c>
       <c r="F521">
-        <v>34.69</v>
+        <v>48.54</v>
       </c>
       <c r="G521">
-        <v>-2.26</v>
+        <v>-0.37</v>
+      </c>
+      <c r="H521" t="s">
+        <v>682</v>
+      </c>
+      <c r="I521" t="s">
+        <v>689</v>
       </c>
       <c r="J521">
-        <v>299.14</v>
+        <v>49.04</v>
       </c>
       <c r="K521">
-        <v>307.89</v>
+        <v>50.13</v>
       </c>
       <c r="L521">
-        <v>306.68</v>
+        <v>50.41</v>
       </c>
       <c r="M521">
-        <v>299.56</v>
+        <v>48.51</v>
       </c>
       <c r="N521">
-        <v>302.56</v>
+        <v>49.54</v>
       </c>
       <c r="O521">
-        <v>308.61</v>
+        <v>50.21</v>
       </c>
     </row>
     <row r="522" spans="1:15">
@@ -25055,43 +25052,37 @@
         <v>593</v>
       </c>
       <c r="C522">
-        <v>49.12</v>
+        <v>45.94</v>
       </c>
       <c r="D522">
-        <v>-2.83</v>
+        <v>-2.01</v>
       </c>
       <c r="E522">
-        <v>-28.53</v>
+        <v>27.2</v>
       </c>
       <c r="F522">
-        <v>48.54</v>
+        <v>60.59</v>
       </c>
       <c r="G522">
-        <v>-0.37</v>
-      </c>
-      <c r="H522" t="s">
-        <v>683</v>
-      </c>
-      <c r="I522" t="s">
-        <v>690</v>
+        <v>0.54</v>
       </c>
       <c r="J522">
-        <v>49.04</v>
+        <v>44.88</v>
       </c>
       <c r="K522">
-        <v>50.13</v>
+        <v>44.36</v>
       </c>
       <c r="L522">
-        <v>50.41</v>
+        <v>43.89</v>
       </c>
       <c r="M522">
-        <v>48.51</v>
+        <v>44.93</v>
       </c>
       <c r="N522">
-        <v>49.54</v>
+        <v>43.09</v>
       </c>
       <c r="O522">
-        <v>50.21</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="523" spans="1:15">
@@ -25102,37 +25093,37 @@
         <v>593</v>
       </c>
       <c r="C523">
-        <v>45.94</v>
+        <v>100.3</v>
       </c>
       <c r="D523">
-        <v>-2.01</v>
+        <v>-3.65</v>
       </c>
       <c r="E523">
-        <v>27.2</v>
+        <v>90.2</v>
       </c>
       <c r="F523">
-        <v>60.59</v>
+        <v>59.63</v>
       </c>
       <c r="G523">
-        <v>0.54</v>
+        <v>0.77</v>
       </c>
       <c r="J523">
-        <v>44.88</v>
+        <v>92.13</v>
       </c>
       <c r="K523">
-        <v>44.36</v>
+        <v>93.91</v>
       </c>
       <c r="L523">
-        <v>43.89</v>
+        <v>97.31</v>
       </c>
       <c r="M523">
-        <v>44.93</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="N523">
-        <v>43.09</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="O523">
-        <v>44.8</v>
+        <v>98.72</v>
       </c>
     </row>
     <row r="524" spans="1:15">
@@ -25143,37 +25134,43 @@
         <v>593</v>
       </c>
       <c r="C524">
-        <v>100.3</v>
+        <v>96.45</v>
       </c>
       <c r="D524">
-        <v>-3.65</v>
+        <v>-1.08</v>
       </c>
       <c r="E524">
-        <v>90.2</v>
+        <v>-31.29</v>
       </c>
       <c r="F524">
-        <v>59.63</v>
+        <v>42.23</v>
       </c>
       <c r="G524">
-        <v>0.77</v>
+        <v>-0.47</v>
+      </c>
+      <c r="H524" t="s">
+        <v>639</v>
+      </c>
+      <c r="I524" t="s">
+        <v>686</v>
       </c>
       <c r="J524">
-        <v>92.13</v>
+        <v>99.34</v>
       </c>
       <c r="K524">
-        <v>93.91</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="L524">
-        <v>97.31</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="M524">
-        <v>92.76000000000001</v>
+        <v>97.37</v>
       </c>
       <c r="N524">
-        <v>95.26000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="O524">
-        <v>98.72</v>
+        <v>99.79000000000001</v>
       </c>
     </row>
     <row r="525" spans="1:15">
@@ -25184,43 +25181,37 @@
         <v>593</v>
       </c>
       <c r="C525">
-        <v>96.45</v>
+        <v>1804</v>
       </c>
       <c r="D525">
-        <v>-1.08</v>
+        <v>0</v>
       </c>
       <c r="E525">
-        <v>-31.29</v>
+        <v>-91.53</v>
       </c>
       <c r="F525">
-        <v>42.23</v>
+        <v>63.46</v>
       </c>
       <c r="G525">
-        <v>-0.47</v>
-      </c>
-      <c r="H525" t="s">
-        <v>639</v>
-      </c>
-      <c r="I525" t="s">
-        <v>687</v>
+        <v>27.6</v>
       </c>
       <c r="J525">
-        <v>99.34</v>
+        <v>1591.94</v>
       </c>
       <c r="K525">
-        <v>99.79000000000001</v>
+        <v>1634.69</v>
       </c>
       <c r="L525">
-        <v>99.79000000000001</v>
+        <v>1646.13</v>
       </c>
       <c r="M525">
-        <v>97.37</v>
+        <v>1609.82</v>
       </c>
       <c r="N525">
-        <v>99.5</v>
+        <v>1640.2</v>
       </c>
       <c r="O525">
-        <v>99.79000000000001</v>
+        <v>1678.37</v>
       </c>
     </row>
     <row r="526" spans="1:15">
@@ -25231,37 +25222,37 @@
         <v>593</v>
       </c>
       <c r="C526">
-        <v>1804</v>
+        <v>1.32</v>
       </c>
       <c r="D526">
-        <v>0</v>
+        <v>-4.35</v>
       </c>
       <c r="E526">
-        <v>-91.53</v>
+        <v>17.96</v>
       </c>
       <c r="F526">
-        <v>63.46</v>
+        <v>44.25</v>
       </c>
       <c r="G526">
-        <v>27.6</v>
+        <v>0.05</v>
       </c>
       <c r="J526">
-        <v>1591.94</v>
+        <v>3.05</v>
       </c>
       <c r="K526">
-        <v>1634.69</v>
+        <v>3.06</v>
       </c>
       <c r="L526">
-        <v>1646.13</v>
+        <v>3.03</v>
       </c>
       <c r="M526">
-        <v>1609.82</v>
+        <v>3.05</v>
       </c>
       <c r="N526">
-        <v>1640.2</v>
+        <v>3.07</v>
       </c>
       <c r="O526">
-        <v>1678.37</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="527" spans="1:15">
@@ -25272,37 +25263,37 @@
         <v>593</v>
       </c>
       <c r="C527">
-        <v>1.32</v>
+        <v>136.1</v>
       </c>
       <c r="D527">
-        <v>-4.35</v>
+        <v>1.64</v>
       </c>
       <c r="E527">
-        <v>17.96</v>
+        <v>219.78</v>
       </c>
       <c r="F527">
-        <v>44.25</v>
+        <v>66.03</v>
       </c>
       <c r="G527">
-        <v>0.05</v>
+        <v>1.68</v>
       </c>
       <c r="J527">
-        <v>3.05</v>
+        <v>117.15</v>
       </c>
       <c r="K527">
-        <v>3.06</v>
+        <v>117.46</v>
       </c>
       <c r="L527">
-        <v>3.03</v>
+        <v>119.15</v>
       </c>
       <c r="M527">
-        <v>3.05</v>
+        <v>117.7</v>
       </c>
       <c r="N527">
-        <v>3.07</v>
+        <v>116.76</v>
       </c>
       <c r="O527">
-        <v>1.3</v>
+        <v>118.22</v>
       </c>
     </row>
     <row r="528" spans="1:15">
@@ -25313,37 +25304,37 @@
         <v>593</v>
       </c>
       <c r="C528">
-        <v>136.1</v>
+        <v>6.15</v>
       </c>
       <c r="D528">
-        <v>1.64</v>
+        <v>-0.65</v>
       </c>
       <c r="E528">
-        <v>219.78</v>
+        <v>15.76</v>
       </c>
       <c r="F528">
-        <v>66.03</v>
+        <v>33.8</v>
       </c>
       <c r="G528">
-        <v>1.68</v>
+        <v>-0.03</v>
       </c>
       <c r="J528">
-        <v>117.15</v>
+        <v>6.74</v>
       </c>
       <c r="K528">
-        <v>117.46</v>
+        <v>6.74</v>
       </c>
       <c r="L528">
-        <v>119.15</v>
+        <v>6.7</v>
       </c>
       <c r="M528">
-        <v>117.7</v>
+        <v>6.74</v>
       </c>
       <c r="N528">
-        <v>116.76</v>
+        <v>6.75</v>
       </c>
       <c r="O528">
-        <v>118.22</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="529" spans="1:15">
@@ -25354,37 +25345,37 @@
         <v>593</v>
       </c>
       <c r="C529">
-        <v>6.15</v>
+        <v>11.43</v>
       </c>
       <c r="D529">
-        <v>-0.65</v>
+        <v>1.33</v>
       </c>
       <c r="E529">
-        <v>15.76</v>
+        <v>33.53</v>
       </c>
       <c r="F529">
-        <v>33.8</v>
+        <v>44.73</v>
       </c>
       <c r="G529">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="J529">
-        <v>6.74</v>
+        <v>11.78</v>
       </c>
       <c r="K529">
-        <v>6.74</v>
+        <v>11.72</v>
       </c>
       <c r="L529">
-        <v>6.7</v>
+        <v>11.89</v>
       </c>
       <c r="M529">
-        <v>6.74</v>
+        <v>11.78</v>
       </c>
       <c r="N529">
-        <v>6.75</v>
+        <v>11.73</v>
       </c>
       <c r="O529">
-        <v>6.71</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="530" spans="1:15">
@@ -25395,37 +25386,43 @@
         <v>593</v>
       </c>
       <c r="C530">
-        <v>11.43</v>
+        <v>0.96</v>
       </c>
       <c r="D530">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="E530">
-        <v>33.53</v>
+        <v>-77.51000000000001</v>
       </c>
       <c r="F530">
-        <v>44.73</v>
+        <v>59.67</v>
       </c>
       <c r="G530">
-        <v>-0.04</v>
+        <v>0.01</v>
+      </c>
+      <c r="H530" t="s">
+        <v>678</v>
+      </c>
+      <c r="I530" t="s">
+        <v>688</v>
       </c>
       <c r="J530">
-        <v>11.78</v>
+        <v>0.97</v>
       </c>
       <c r="K530">
-        <v>11.72</v>
+        <v>0.97</v>
       </c>
       <c r="L530">
-        <v>11.89</v>
+        <v>0.95</v>
       </c>
       <c r="M530">
-        <v>11.78</v>
+        <v>0.97</v>
       </c>
       <c r="N530">
-        <v>11.73</v>
+        <v>0.96</v>
       </c>
       <c r="O530">
-        <v>11.64</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="531" spans="1:15">
@@ -25436,43 +25433,37 @@
         <v>593</v>
       </c>
       <c r="C531">
-        <v>0.96</v>
+        <v>54</v>
       </c>
       <c r="D531">
-        <v>1.05</v>
+        <v>-2.96</v>
       </c>
       <c r="E531">
-        <v>-77.51000000000001</v>
+        <v>12.73</v>
       </c>
       <c r="F531">
-        <v>59.67</v>
+        <v>30.77</v>
       </c>
       <c r="G531">
-        <v>0.01</v>
-      </c>
-      <c r="H531" t="s">
-        <v>678</v>
-      </c>
-      <c r="I531" t="s">
-        <v>689</v>
+        <v>-0.29</v>
       </c>
       <c r="J531">
-        <v>0.97</v>
+        <v>61.3</v>
       </c>
       <c r="K531">
-        <v>0.97</v>
+        <v>61.12</v>
       </c>
       <c r="L531">
-        <v>0.95</v>
+        <v>59.97</v>
       </c>
       <c r="M531">
-        <v>0.97</v>
+        <v>61.17</v>
       </c>
       <c r="N531">
-        <v>0.96</v>
+        <v>60.77</v>
       </c>
       <c r="O531">
-        <v>0.9399999999999999</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="532" spans="1:15">
@@ -25483,37 +25474,37 @@
         <v>593</v>
       </c>
       <c r="C532">
-        <v>54</v>
+        <v>411.5</v>
       </c>
       <c r="D532">
-        <v>-2.96</v>
+        <v>-0.18</v>
       </c>
       <c r="E532">
-        <v>12.73</v>
+        <v>11.86</v>
       </c>
       <c r="F532">
-        <v>30.77</v>
+        <v>32.34</v>
       </c>
       <c r="G532">
-        <v>-0.29</v>
+        <v>-2.86</v>
       </c>
       <c r="J532">
-        <v>61.3</v>
+        <v>443.35</v>
       </c>
       <c r="K532">
-        <v>61.12</v>
+        <v>437.35</v>
       </c>
       <c r="L532">
-        <v>59.97</v>
+        <v>429.84</v>
       </c>
       <c r="M532">
-        <v>61.17</v>
+        <v>448.38</v>
       </c>
       <c r="N532">
-        <v>60.77</v>
+        <v>440.58</v>
       </c>
       <c r="O532">
-        <v>57.36</v>
+        <v>435.39</v>
       </c>
     </row>
     <row r="533" spans="1:15">
@@ -25524,37 +25515,37 @@
         <v>593</v>
       </c>
       <c r="C533">
-        <v>411.5</v>
+        <v>3.85</v>
       </c>
       <c r="D533">
-        <v>-0.18</v>
+        <v>-2.04</v>
       </c>
       <c r="E533">
-        <v>11.86</v>
+        <v>23.48</v>
       </c>
       <c r="F533">
-        <v>32.34</v>
+        <v>35.82</v>
       </c>
       <c r="G533">
-        <v>-2.86</v>
+        <v>-0</v>
       </c>
       <c r="J533">
-        <v>443.35</v>
+        <v>4.26</v>
       </c>
       <c r="K533">
-        <v>437.35</v>
+        <v>4.29</v>
       </c>
       <c r="L533">
-        <v>429.84</v>
+        <v>4.2</v>
       </c>
       <c r="M533">
-        <v>448.38</v>
+        <v>4.29</v>
       </c>
       <c r="N533">
-        <v>440.58</v>
+        <v>4.25</v>
       </c>
       <c r="O533">
-        <v>435.39</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="534" spans="1:15">
@@ -25565,37 +25556,43 @@
         <v>593</v>
       </c>
       <c r="C534">
-        <v>3.85</v>
+        <v>2.1</v>
       </c>
       <c r="D534">
-        <v>-2.04</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E534">
-        <v>23.48</v>
+        <v>4.49</v>
       </c>
       <c r="F534">
-        <v>35.82</v>
+        <v>33.17</v>
       </c>
       <c r="G534">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="H534" t="s">
+        <v>594</v>
+      </c>
+      <c r="I534" t="s">
+        <v>686</v>
       </c>
       <c r="J534">
-        <v>4.26</v>
+        <v>2.54</v>
       </c>
       <c r="K534">
-        <v>4.29</v>
+        <v>2.38</v>
       </c>
       <c r="L534">
-        <v>4.2</v>
+        <v>2.21</v>
       </c>
       <c r="M534">
-        <v>4.29</v>
+        <v>2.43</v>
       </c>
       <c r="N534">
-        <v>4.25</v>
+        <v>2.32</v>
       </c>
       <c r="O534">
-        <v>3.92</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="535" spans="1:15">
@@ -25606,43 +25603,37 @@
         <v>593</v>
       </c>
       <c r="C535">
-        <v>2.1</v>
+        <v>304.25</v>
       </c>
       <c r="D535">
-        <v>-0.9399999999999999</v>
+        <v>-3.26</v>
       </c>
       <c r="E535">
-        <v>4.49</v>
+        <v>5.56</v>
       </c>
       <c r="F535">
-        <v>33.17</v>
+        <v>74.48</v>
       </c>
       <c r="G535">
-        <v>0</v>
-      </c>
-      <c r="H535" t="s">
-        <v>594</v>
-      </c>
-      <c r="I535" t="s">
-        <v>687</v>
+        <v>5.25</v>
       </c>
       <c r="J535">
-        <v>2.54</v>
+        <v>254.99</v>
       </c>
       <c r="K535">
-        <v>2.38</v>
+        <v>255.87</v>
       </c>
       <c r="L535">
-        <v>2.21</v>
+        <v>254.53</v>
       </c>
       <c r="M535">
-        <v>2.43</v>
+        <v>255.48</v>
       </c>
       <c r="N535">
-        <v>2.32</v>
+        <v>255.21</v>
       </c>
       <c r="O535">
-        <v>2.11</v>
+        <v>267.53</v>
       </c>
     </row>
     <row r="536" spans="1:15">
@@ -25653,37 +25644,43 @@
         <v>593</v>
       </c>
       <c r="C536">
-        <v>304.25</v>
+        <v>7.95</v>
       </c>
       <c r="D536">
-        <v>-3.26</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E536">
-        <v>5.56</v>
+        <v>357.77</v>
       </c>
       <c r="F536">
-        <v>74.48</v>
+        <v>63.9</v>
       </c>
       <c r="G536">
-        <v>5.25</v>
+        <v>0.11</v>
+      </c>
+      <c r="H536" t="s">
+        <v>603</v>
+      </c>
+      <c r="I536" t="s">
+        <v>687</v>
       </c>
       <c r="J536">
-        <v>254.99</v>
+        <v>8.32</v>
       </c>
       <c r="K536">
-        <v>255.87</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L536">
-        <v>254.53</v>
+        <v>8.23</v>
       </c>
       <c r="M536">
-        <v>255.48</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="N536">
-        <v>255.21</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="O536">
-        <v>267.53</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="537" spans="1:15">
@@ -25694,43 +25691,37 @@
         <v>593</v>
       </c>
       <c r="C537">
-        <v>7.95</v>
+        <v>6.62</v>
       </c>
       <c r="D537">
-        <v>9.960000000000001</v>
+        <v>-0.75</v>
       </c>
       <c r="E537">
-        <v>357.77</v>
+        <v>-35.74</v>
       </c>
       <c r="F537">
-        <v>63.9</v>
+        <v>55.97</v>
       </c>
       <c r="G537">
-        <v>0.11</v>
-      </c>
-      <c r="H537" t="s">
-        <v>603</v>
-      </c>
-      <c r="I537" t="s">
-        <v>688</v>
+        <v>0.06</v>
       </c>
       <c r="J537">
-        <v>8.32</v>
+        <v>6.61</v>
       </c>
       <c r="K537">
-        <v>8.460000000000001</v>
+        <v>6.55</v>
       </c>
       <c r="L537">
-        <v>8.23</v>
+        <v>6.41</v>
       </c>
       <c r="M537">
-        <v>8.380000000000001</v>
+        <v>6.57</v>
       </c>
       <c r="N537">
-        <v>8.390000000000001</v>
+        <v>6.52</v>
       </c>
       <c r="O537">
-        <v>7.42</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="538" spans="1:15">
@@ -25741,37 +25732,37 @@
         <v>593</v>
       </c>
       <c r="C538">
-        <v>6.62</v>
+        <v>1653</v>
       </c>
       <c r="D538">
-        <v>-0.75</v>
+        <v>-0.18</v>
       </c>
       <c r="E538">
-        <v>-35.74</v>
+        <v>-49.93</v>
       </c>
       <c r="F538">
-        <v>55.97</v>
+        <v>52.64</v>
       </c>
       <c r="G538">
-        <v>0.06</v>
+        <v>-11.13</v>
       </c>
       <c r="J538">
-        <v>6.61</v>
+        <v>1537.19</v>
       </c>
       <c r="K538">
-        <v>6.55</v>
+        <v>1511.01</v>
       </c>
       <c r="L538">
-        <v>6.41</v>
+        <v>1533.52</v>
       </c>
       <c r="M538">
-        <v>6.57</v>
+        <v>1543.53</v>
       </c>
       <c r="N538">
-        <v>6.52</v>
+        <v>1531.51</v>
       </c>
       <c r="O538">
-        <v>6.5</v>
+        <v>1528.06</v>
       </c>
     </row>
     <row r="539" spans="1:15">
@@ -25782,37 +25773,43 @@
         <v>593</v>
       </c>
       <c r="C539">
-        <v>1653</v>
+        <v>23.76</v>
       </c>
       <c r="D539">
-        <v>-0.18</v>
+        <v>-2.06</v>
       </c>
       <c r="E539">
-        <v>-49.93</v>
+        <v>8.4</v>
       </c>
       <c r="F539">
-        <v>52.64</v>
+        <v>39.21</v>
       </c>
       <c r="G539">
-        <v>-11.13</v>
+        <v>0.13</v>
+      </c>
+      <c r="H539" t="s">
+        <v>600</v>
+      </c>
+      <c r="I539" t="s">
+        <v>686</v>
       </c>
       <c r="J539">
-        <v>1537.19</v>
+        <v>27.02</v>
       </c>
       <c r="K539">
-        <v>1511.01</v>
+        <v>25.99</v>
       </c>
       <c r="L539">
-        <v>1533.52</v>
+        <v>24.09</v>
       </c>
       <c r="M539">
-        <v>1543.53</v>
+        <v>26.24</v>
       </c>
       <c r="N539">
-        <v>1531.51</v>
+        <v>24.32</v>
       </c>
       <c r="O539">
-        <v>1528.06</v>
+        <v>24.24</v>
       </c>
     </row>
     <row r="540" spans="1:15">
@@ -25823,43 +25820,37 @@
         <v>593</v>
       </c>
       <c r="C540">
-        <v>23.76</v>
+        <v>92.05</v>
       </c>
       <c r="D540">
-        <v>-2.06</v>
+        <v>-2.44</v>
       </c>
       <c r="E540">
-        <v>8.4</v>
+        <v>7.93</v>
       </c>
       <c r="F540">
-        <v>39.21</v>
+        <v>24.98</v>
       </c>
       <c r="G540">
-        <v>0.13</v>
-      </c>
-      <c r="H540" t="s">
-        <v>600</v>
-      </c>
-      <c r="I540" t="s">
-        <v>687</v>
+        <v>0.15</v>
       </c>
       <c r="J540">
-        <v>27.02</v>
+        <v>117.22</v>
       </c>
       <c r="K540">
-        <v>25.99</v>
+        <v>110.38</v>
       </c>
       <c r="L540">
-        <v>24.09</v>
+        <v>100.42</v>
       </c>
       <c r="M540">
-        <v>26.24</v>
+        <v>114.31</v>
       </c>
       <c r="N540">
-        <v>24.32</v>
+        <v>106.53</v>
       </c>
       <c r="O540">
-        <v>24.24</v>
+        <v>95.98</v>
       </c>
     </row>
     <row r="541" spans="1:15">
@@ -25870,37 +25861,43 @@
         <v>593</v>
       </c>
       <c r="C541">
-        <v>92.05</v>
+        <v>1.71</v>
       </c>
       <c r="D541">
-        <v>-2.44</v>
+        <v>-3.93</v>
       </c>
       <c r="E541">
-        <v>7.93</v>
+        <v>-19.22</v>
       </c>
       <c r="F541">
-        <v>24.98</v>
+        <v>37.64</v>
       </c>
       <c r="G541">
-        <v>0.15</v>
+        <v>0.01</v>
+      </c>
+      <c r="H541" t="s">
+        <v>594</v>
+      </c>
+      <c r="I541" t="s">
+        <v>686</v>
       </c>
       <c r="J541">
-        <v>117.22</v>
+        <v>2.07</v>
       </c>
       <c r="K541">
-        <v>110.38</v>
+        <v>1.97</v>
       </c>
       <c r="L541">
-        <v>100.42</v>
+        <v>1.83</v>
       </c>
       <c r="M541">
-        <v>114.31</v>
+        <v>2.03</v>
       </c>
       <c r="N541">
-        <v>106.53</v>
+        <v>1.84</v>
       </c>
       <c r="O541">
-        <v>95.98</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="542" spans="1:15">
@@ -25911,43 +25908,43 @@
         <v>593</v>
       </c>
       <c r="C542">
-        <v>1.71</v>
+        <v>290</v>
       </c>
       <c r="D542">
-        <v>-3.93</v>
+        <v>-2.44</v>
       </c>
       <c r="E542">
-        <v>-19.22</v>
+        <v>-1.7</v>
       </c>
       <c r="F542">
-        <v>37.64</v>
+        <v>46.21</v>
       </c>
       <c r="G542">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H542" t="s">
-        <v>594</v>
+        <v>683</v>
       </c>
       <c r="I542" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J542">
-        <v>2.07</v>
+        <v>298.64</v>
       </c>
       <c r="K542">
-        <v>1.97</v>
+        <v>321.38</v>
       </c>
       <c r="L542">
-        <v>1.83</v>
+        <v>295</v>
       </c>
       <c r="M542">
-        <v>2.03</v>
+        <v>282.29</v>
       </c>
       <c r="N542">
-        <v>1.84</v>
+        <v>308.09</v>
       </c>
       <c r="O542">
-        <v>1.77</v>
+        <v>294.68</v>
       </c>
     </row>
     <row r="543" spans="1:15">
@@ -25958,43 +25955,43 @@
         <v>593</v>
       </c>
       <c r="C543">
-        <v>290</v>
+        <v>9.25</v>
       </c>
       <c r="D543">
-        <v>-2.44</v>
+        <v>-5.42</v>
       </c>
       <c r="E543">
-        <v>-1.7</v>
+        <v>-26.37</v>
       </c>
       <c r="F543">
-        <v>46.21</v>
+        <v>50.99</v>
       </c>
       <c r="G543">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="H543" t="s">
-        <v>684</v>
+        <v>643</v>
       </c>
       <c r="I543" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="J543">
-        <v>298.64</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="K543">
-        <v>321.38</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="L543">
-        <v>295</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="M543">
-        <v>282.29</v>
+        <v>8.94</v>
       </c>
       <c r="N543">
-        <v>308.09</v>
+        <v>9.27</v>
       </c>
       <c r="O543">
-        <v>294.68</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="544" spans="1:15">
@@ -26005,43 +26002,37 @@
         <v>593</v>
       </c>
       <c r="C544">
-        <v>9.25</v>
+        <v>11.8</v>
       </c>
       <c r="D544">
-        <v>-5.42</v>
+        <v>-0.76</v>
       </c>
       <c r="E544">
-        <v>-26.37</v>
+        <v>-1.87</v>
       </c>
       <c r="F544">
-        <v>50.99</v>
+        <v>34.41</v>
       </c>
       <c r="G544">
-        <v>0.03</v>
-      </c>
-      <c r="H544" t="s">
-        <v>643</v>
-      </c>
-      <c r="I544" t="s">
-        <v>690</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J544">
-        <v>8.869999999999999</v>
+        <v>14.05</v>
       </c>
       <c r="K544">
-        <v>9.220000000000001</v>
+        <v>13.33</v>
       </c>
       <c r="L544">
-        <v>9.359999999999999</v>
+        <v>12.97</v>
       </c>
       <c r="M544">
-        <v>8.94</v>
+        <v>14.56</v>
       </c>
       <c r="N544">
-        <v>9.27</v>
+        <v>13.38</v>
       </c>
       <c r="O544">
-        <v>9.48</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="545" spans="1:15">
@@ -26052,37 +26043,37 @@
         <v>593</v>
       </c>
       <c r="C545">
-        <v>11.8</v>
+        <v>1.42</v>
       </c>
       <c r="D545">
-        <v>-0.76</v>
+        <v>-1.39</v>
       </c>
       <c r="E545">
-        <v>-1.87</v>
+        <v>-56.7</v>
       </c>
       <c r="F545">
-        <v>34.41</v>
+        <v>44.41</v>
       </c>
       <c r="G545">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="J545">
-        <v>14.05</v>
+        <v>1.65</v>
       </c>
       <c r="K545">
-        <v>13.33</v>
+        <v>1.63</v>
       </c>
       <c r="L545">
-        <v>12.97</v>
+        <v>1.49</v>
       </c>
       <c r="M545">
-        <v>14.56</v>
+        <v>1.64</v>
       </c>
       <c r="N545">
-        <v>13.38</v>
+        <v>1.53</v>
       </c>
       <c r="O545">
-        <v>13.15</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="546" spans="1:15">
@@ -26093,37 +26084,37 @@
         <v>593</v>
       </c>
       <c r="C546">
-        <v>1.42</v>
+        <v>30.24</v>
       </c>
       <c r="D546">
-        <v>-1.39</v>
+        <v>-0.66</v>
       </c>
       <c r="E546">
-        <v>-56.7</v>
+        <v>-19.08</v>
       </c>
       <c r="F546">
-        <v>44.41</v>
+        <v>37.91</v>
       </c>
       <c r="G546">
-        <v>0.01</v>
+        <v>-0.14</v>
       </c>
       <c r="J546">
-        <v>1.65</v>
+        <v>32.34</v>
       </c>
       <c r="K546">
-        <v>1.63</v>
+        <v>32.24</v>
       </c>
       <c r="L546">
-        <v>1.49</v>
+        <v>32.33</v>
       </c>
       <c r="M546">
-        <v>1.64</v>
+        <v>32.36</v>
       </c>
       <c r="N546">
-        <v>1.53</v>
+        <v>32.19</v>
       </c>
       <c r="O546">
-        <v>1.45</v>
+        <v>32.39</v>
       </c>
     </row>
     <row r="547" spans="1:15">
@@ -26134,37 +26125,37 @@
         <v>593</v>
       </c>
       <c r="C547">
-        <v>30.24</v>
+        <v>11.56</v>
       </c>
       <c r="D547">
-        <v>-0.66</v>
+        <v>-0.34</v>
       </c>
       <c r="E547">
-        <v>-19.08</v>
+        <v>-22.13</v>
       </c>
       <c r="F547">
-        <v>37.91</v>
+        <v>41.36</v>
       </c>
       <c r="G547">
-        <v>-0.14</v>
+        <v>0.01</v>
       </c>
       <c r="J547">
-        <v>32.34</v>
+        <v>12.93</v>
       </c>
       <c r="K547">
-        <v>32.24</v>
+        <v>12.45</v>
       </c>
       <c r="L547">
-        <v>32.33</v>
+        <v>12.09</v>
       </c>
       <c r="M547">
-        <v>32.36</v>
+        <v>12.76</v>
       </c>
       <c r="N547">
-        <v>32.19</v>
+        <v>12.22</v>
       </c>
       <c r="O547">
-        <v>32.39</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="548" spans="1:15">
@@ -26175,37 +26166,43 @@
         <v>593</v>
       </c>
       <c r="C548">
-        <v>11.56</v>
+        <v>1.29</v>
       </c>
       <c r="D548">
-        <v>-0.34</v>
+        <v>-1.53</v>
       </c>
       <c r="E548">
-        <v>-22.13</v>
+        <v>8.33</v>
       </c>
       <c r="F548">
-        <v>41.36</v>
+        <v>38.22</v>
       </c>
       <c r="G548">
-        <v>0.01</v>
+        <v>0</v>
+      </c>
+      <c r="H548" t="s">
+        <v>594</v>
+      </c>
+      <c r="I548" t="s">
+        <v>686</v>
       </c>
       <c r="J548">
-        <v>12.93</v>
+        <v>1.45</v>
       </c>
       <c r="K548">
-        <v>12.45</v>
+        <v>1.41</v>
       </c>
       <c r="L548">
-        <v>12.09</v>
+        <v>1.36</v>
       </c>
       <c r="M548">
-        <v>12.76</v>
+        <v>1.43</v>
       </c>
       <c r="N548">
-        <v>12.22</v>
+        <v>1.39</v>
       </c>
       <c r="O548">
-        <v>11.61</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="549" spans="1:15">
@@ -26216,43 +26213,43 @@
         <v>593</v>
       </c>
       <c r="C549">
-        <v>1.29</v>
+        <v>70.25</v>
       </c>
       <c r="D549">
-        <v>-1.53</v>
+        <v>-2.02</v>
       </c>
       <c r="E549">
-        <v>8.33</v>
+        <v>-31.88</v>
       </c>
       <c r="F549">
-        <v>38.22</v>
+        <v>40.52</v>
       </c>
       <c r="G549">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="H549" t="s">
         <v>594</v>
       </c>
       <c r="I549" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J549">
-        <v>1.45</v>
+        <v>80.69</v>
       </c>
       <c r="K549">
-        <v>1.41</v>
+        <v>82.11</v>
       </c>
       <c r="L549">
-        <v>1.36</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="M549">
-        <v>1.43</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="N549">
-        <v>1.39</v>
+        <v>76.47</v>
       </c>
       <c r="O549">
-        <v>1.3</v>
+        <v>71.28</v>
       </c>
     </row>
     <row r="550" spans="1:15">
@@ -26263,43 +26260,43 @@
         <v>593</v>
       </c>
       <c r="C550">
-        <v>70.25</v>
+        <v>92.95</v>
       </c>
       <c r="D550">
-        <v>-2.02</v>
+        <v>-1.95</v>
       </c>
       <c r="E550">
-        <v>-31.88</v>
+        <v>-11.23</v>
       </c>
       <c r="F550">
-        <v>40.52</v>
+        <v>50.76</v>
       </c>
       <c r="G550">
-        <v>0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="H550" t="s">
-        <v>594</v>
+        <v>684</v>
       </c>
       <c r="I550" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="J550">
-        <v>80.69</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="K550">
-        <v>82.11</v>
+        <v>96.67</v>
       </c>
       <c r="L550">
-        <v>76.34999999999999</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="M550">
-        <v>82.20999999999999</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="N550">
-        <v>76.47</v>
+        <v>96.14</v>
       </c>
       <c r="O550">
-        <v>71.28</v>
+        <v>93.52</v>
       </c>
     </row>
     <row r="551" spans="1:15">
@@ -26310,43 +26307,37 @@
         <v>593</v>
       </c>
       <c r="C551">
-        <v>92.95</v>
+        <v>34.6</v>
       </c>
       <c r="D551">
-        <v>-1.95</v>
+        <v>4.34</v>
       </c>
       <c r="E551">
-        <v>-11.23</v>
+        <v>25.71</v>
       </c>
       <c r="F551">
-        <v>50.76</v>
+        <v>71.87</v>
       </c>
       <c r="G551">
-        <v>-0.13</v>
-      </c>
-      <c r="H551" t="s">
-        <v>685</v>
-      </c>
-      <c r="I551" t="s">
-        <v>690</v>
+        <v>0.44</v>
       </c>
       <c r="J551">
-        <v>93.54000000000001</v>
+        <v>24.12</v>
       </c>
       <c r="K551">
-        <v>96.67</v>
+        <v>25.71</v>
       </c>
       <c r="L551">
-        <v>93.48999999999999</v>
+        <v>30.36</v>
       </c>
       <c r="M551">
-        <v>90.56999999999999</v>
+        <v>24.42</v>
       </c>
       <c r="N551">
-        <v>96.14</v>
+        <v>27.22</v>
       </c>
       <c r="O551">
-        <v>93.52</v>
+        <v>30.16</v>
       </c>
     </row>
     <row r="552" spans="1:15">
@@ -26357,37 +26348,37 @@
         <v>593</v>
       </c>
       <c r="C552">
-        <v>34.6</v>
+        <v>480.25</v>
       </c>
       <c r="D552">
-        <v>4.34</v>
+        <v>0.47</v>
       </c>
       <c r="E552">
-        <v>25.71</v>
+        <v>-45.1</v>
       </c>
       <c r="F552">
-        <v>71.87</v>
+        <v>43.96</v>
       </c>
       <c r="G552">
-        <v>0.44</v>
+        <v>3.14</v>
       </c>
       <c r="J552">
-        <v>24.12</v>
+        <v>529.86</v>
       </c>
       <c r="K552">
-        <v>25.71</v>
+        <v>529.86</v>
       </c>
       <c r="L552">
-        <v>30.36</v>
+        <v>514.73</v>
       </c>
       <c r="M552">
-        <v>24.42</v>
+        <v>529.61</v>
       </c>
       <c r="N552">
-        <v>27.22</v>
+        <v>530.04</v>
       </c>
       <c r="O552">
-        <v>30.16</v>
+        <v>455.18</v>
       </c>
     </row>
     <row r="553" spans="1:15">
@@ -26398,37 +26389,37 @@
         <v>593</v>
       </c>
       <c r="C553">
-        <v>480.25</v>
+        <v>6.12</v>
       </c>
       <c r="D553">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="E553">
-        <v>-45.1</v>
+        <v>223.23</v>
       </c>
       <c r="F553">
-        <v>43.96</v>
+        <v>43.74</v>
       </c>
       <c r="G553">
-        <v>3.14</v>
+        <v>-0.01</v>
       </c>
       <c r="J553">
-        <v>529.86</v>
+        <v>6.59</v>
       </c>
       <c r="K553">
-        <v>529.86</v>
+        <v>6.52</v>
       </c>
       <c r="L553">
-        <v>514.73</v>
+        <v>6.25</v>
       </c>
       <c r="M553">
-        <v>529.61</v>
+        <v>6.65</v>
       </c>
       <c r="N553">
-        <v>530.04</v>
+        <v>6.5</v>
       </c>
       <c r="O553">
-        <v>455.18</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="554" spans="1:15">
@@ -26439,37 +26430,37 @@
         <v>593</v>
       </c>
       <c r="C554">
-        <v>6.12</v>
+        <v>24.42</v>
       </c>
       <c r="D554">
         <v>0.33</v>
       </c>
       <c r="E554">
-        <v>223.23</v>
+        <v>161.9</v>
       </c>
       <c r="F554">
-        <v>43.74</v>
+        <v>45.09</v>
       </c>
       <c r="G554">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="J554">
-        <v>6.59</v>
+        <v>25.76</v>
       </c>
       <c r="K554">
-        <v>6.52</v>
+        <v>25.31</v>
       </c>
       <c r="L554">
-        <v>6.25</v>
+        <v>25.25</v>
       </c>
       <c r="M554">
-        <v>6.65</v>
+        <v>26</v>
       </c>
       <c r="N554">
-        <v>6.5</v>
+        <v>25.25</v>
       </c>
       <c r="O554">
-        <v>6.28</v>
+        <v>25.12</v>
       </c>
     </row>
     <row r="555" spans="1:15">
@@ -26480,37 +26471,37 @@
         <v>593</v>
       </c>
       <c r="C555">
-        <v>24.42</v>
+        <v>26.4</v>
       </c>
       <c r="D555">
-        <v>0.33</v>
+        <v>1.54</v>
       </c>
       <c r="E555">
-        <v>161.9</v>
+        <v>-18.13</v>
       </c>
       <c r="F555">
-        <v>45.09</v>
+        <v>42.75</v>
       </c>
       <c r="G555">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="J555">
-        <v>25.76</v>
+        <v>31.5</v>
       </c>
       <c r="K555">
-        <v>25.31</v>
+        <v>28.22</v>
       </c>
       <c r="L555">
-        <v>25.25</v>
+        <v>28.47</v>
       </c>
       <c r="M555">
-        <v>26</v>
+        <v>31.64</v>
       </c>
       <c r="N555">
-        <v>25.25</v>
+        <v>28.57</v>
       </c>
       <c r="O555">
-        <v>25.12</v>
+        <v>28.43</v>
       </c>
     </row>
     <row r="556" spans="1:15">
@@ -26521,37 +26512,43 @@
         <v>593</v>
       </c>
       <c r="C556">
-        <v>26.4</v>
+        <v>2.64</v>
       </c>
       <c r="D556">
-        <v>1.54</v>
+        <v>-1.12</v>
       </c>
       <c r="E556">
-        <v>-18.13</v>
+        <v>-25.44</v>
       </c>
       <c r="F556">
-        <v>42.75</v>
+        <v>42.55</v>
       </c>
       <c r="G556">
-        <v>-0.05</v>
+        <v>0</v>
+      </c>
+      <c r="H556" t="s">
+        <v>594</v>
+      </c>
+      <c r="I556" t="s">
+        <v>686</v>
       </c>
       <c r="J556">
-        <v>31.5</v>
+        <v>2.76</v>
       </c>
       <c r="K556">
-        <v>28.22</v>
+        <v>2.76</v>
       </c>
       <c r="L556">
-        <v>28.47</v>
+        <v>2.7</v>
       </c>
       <c r="M556">
-        <v>31.64</v>
+        <v>2.77</v>
       </c>
       <c r="N556">
-        <v>28.57</v>
+        <v>2.74</v>
       </c>
       <c r="O556">
-        <v>28.43</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="557" spans="1:15">
@@ -26562,43 +26559,37 @@
         <v>593</v>
       </c>
       <c r="C557">
-        <v>2.64</v>
+        <v>23.96</v>
       </c>
       <c r="D557">
-        <v>-1.12</v>
+        <v>-0.66</v>
       </c>
       <c r="E557">
-        <v>-25.44</v>
+        <v>-44.55</v>
       </c>
       <c r="F557">
-        <v>42.55</v>
+        <v>44.92</v>
       </c>
       <c r="G557">
-        <v>0</v>
-      </c>
-      <c r="H557" t="s">
-        <v>594</v>
-      </c>
-      <c r="I557" t="s">
-        <v>687</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J557">
-        <v>2.76</v>
+        <v>25.88</v>
       </c>
       <c r="K557">
-        <v>2.76</v>
+        <v>25.71</v>
       </c>
       <c r="L557">
-        <v>2.7</v>
+        <v>24.86</v>
       </c>
       <c r="M557">
-        <v>2.77</v>
+        <v>25.99</v>
       </c>
       <c r="N557">
-        <v>2.74</v>
+        <v>25.28</v>
       </c>
       <c r="O557">
-        <v>2.65</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="558" spans="1:15">
@@ -26609,37 +26600,37 @@
         <v>593</v>
       </c>
       <c r="C558">
-        <v>23.96</v>
+        <v>1.93</v>
       </c>
       <c r="D558">
-        <v>-0.66</v>
+        <v>0</v>
       </c>
       <c r="E558">
-        <v>-44.55</v>
+        <v>-21.23</v>
       </c>
       <c r="F558">
-        <v>44.92</v>
+        <v>34.47</v>
       </c>
       <c r="G558">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="J558">
-        <v>25.88</v>
+        <v>2.25</v>
       </c>
       <c r="K558">
-        <v>25.71</v>
+        <v>2.15</v>
       </c>
       <c r="L558">
-        <v>24.86</v>
+        <v>2.03</v>
       </c>
       <c r="M558">
-        <v>25.99</v>
+        <v>2.19</v>
       </c>
       <c r="N558">
-        <v>25.28</v>
+        <v>2.06</v>
       </c>
       <c r="O558">
-        <v>24.69</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="559" spans="1:15">
@@ -26650,37 +26641,37 @@
         <v>593</v>
       </c>
       <c r="C559">
-        <v>1.93</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="D559">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="E559">
-        <v>-21.23</v>
+        <v>6.2</v>
       </c>
       <c r="F559">
-        <v>34.47</v>
+        <v>41.61</v>
       </c>
       <c r="G559">
-        <v>0</v>
+        <v>-0.49</v>
       </c>
       <c r="J559">
-        <v>2.25</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="K559">
-        <v>2.15</v>
+        <v>92.92</v>
       </c>
       <c r="L559">
-        <v>2.03</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="M559">
-        <v>2.19</v>
+        <v>90.58</v>
       </c>
       <c r="N559">
-        <v>2.06</v>
+        <v>92.94</v>
       </c>
       <c r="O559">
-        <v>1.95</v>
+        <v>93.43000000000001</v>
       </c>
     </row>
     <row r="560" spans="1:15">
@@ -26870,10 +26861,10 @@
         <v>-0</v>
       </c>
       <c r="H564" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="I564" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J564">
         <v>25.19</v>
@@ -27002,7 +26993,7 @@
         <v>610</v>
       </c>
       <c r="I567" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J567">
         <v>1.6</v>
@@ -27049,7 +27040,7 @@
         <v>615</v>
       </c>
       <c r="I568" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J568">
         <v>229.79</v>
@@ -27424,7 +27415,7 @@
         <v>610</v>
       </c>
       <c r="I577" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J577">
         <v>15.69</v>
